--- a/00data/sankey_files/Total Sankeys.xlsx
+++ b/00data/sankey_files/Total Sankeys.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/charlottewestenberg/Thesis/00data/sankey_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{137B3150-262F-BC40-8CAC-B5A63D2E63F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B3A80E84-7DBB-3844-9ECE-AA59B4628296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{6CE99965-ED79-8449-8BF0-6D9AFDCB5B89}"/>
   </bookViews>
